--- a/inputs/data_symbols_TD/10_LTAN06_800km_HOT_MY_ALL_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/10_LTAN06_800km_HOT_MY_ALL_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82620F1F-8474-48A6-B8EE-B226B0CACFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85D159B1-F452-484A-B692-32DB68F7C193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{C0E98C8F-BF42-442E-B248-E574F10D4F26}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{CC77782E-B6AE-4BCD-9A3A-99045480BBC6}"/>
   </bookViews>
   <sheets>
     <sheet name="10_LTAN06_800km_HOT_MY_ALL_HEAT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944D4DEF-5BDA-44DE-BC5B-38F5E8402C23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82695578-993A-4574-BBB1-D3D440E83272}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>119.30500000000001</v>
+        <v>109.14879999999999</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>119.30500000000001</v>
+        <v>109.14879999999999</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>119.3049</v>
+        <v>109.14870000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>119.3047</v>
+        <v>109.1485</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>119.3044</v>
+        <v>109.1482</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>119.304</v>
+        <v>109.1478</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>119.3035</v>
+        <v>109.1473</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>119.303</v>
+        <v>109.1468</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>119.3023</v>
+        <v>109.1461</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>119.3015</v>
+        <v>109.14530000000001</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>119.30070000000001</v>
+        <v>109.14449999999999</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>119.2997</v>
+        <v>109.14360000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>119.2987</v>
+        <v>109.1426</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>119.2976</v>
+        <v>109.14149999999999</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>119.29649999999999</v>
+        <v>109.1404</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>119.2953</v>
+        <v>109.1392</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>119.294</v>
+        <v>109.1379</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>119.29259999999999</v>
+        <v>109.1366</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>119.2912</v>
+        <v>109.1352</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>119.2898</v>
+        <v>109.1337</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>119.28830000000001</v>
+        <v>109.1323</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>119.2868</v>
+        <v>109.1307</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>119.28530000000001</v>
+        <v>109.1292</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>119.2837</v>
+        <v>109.1276</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>119.2822</v>
+        <v>109.126</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>119.28060000000001</v>
+        <v>109.12430000000001</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>119.279</v>
+        <v>109.12269999999999</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>119.2774</v>
+        <v>109.121</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>119.2757</v>
+        <v>109.1193</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>119.2741</v>
+        <v>109.1176</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>119.27249999999999</v>
+        <v>109.1159</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>119.27079999999999</v>
+        <v>109.1142</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>119.2692</v>
+        <v>109.1125</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>119.2676</v>
+        <v>109.1108</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>119.2659</v>
+        <v>109.10899999999999</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>119.26430000000001</v>
+        <v>109.1073</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>119.2627</v>
+        <v>109.1056</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>119.2611</v>
+        <v>109.1039</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>119.2595</v>
+        <v>109.1022</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>119.25790000000001</v>
+        <v>109.10039999999999</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>119.2563</v>
+        <v>109.09869999999999</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>119.2547</v>
+        <v>109.09699999999999</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>119.2531</v>
+        <v>109.0954</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>119.2516</v>
+        <v>109.0937</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>119.25</v>
+        <v>109.092</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>119.24850000000001</v>
+        <v>109.0904</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>119.2469</v>
+        <v>109.08880000000001</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>119.2454</v>
+        <v>109.0872</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>119.244</v>
+        <v>109.0857</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>119.24250000000001</v>
+        <v>109.0842</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>119.24120000000001</v>
+        <v>109.08280000000001</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>119.2398</v>
+        <v>109.0814</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>119.23860000000001</v>
+        <v>109.0801</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>119.23739999999999</v>
+        <v>109.0789</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>119.2363</v>
+        <v>109.0778</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>119.2353</v>
+        <v>109.0767</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>119.2345</v>
+        <v>109.0758</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>119.2337</v>
+        <v>109.075</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>119.23309999999999</v>
+        <v>109.07429999999999</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>119.23260000000001</v>
+        <v>109.0737</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>119.2323</v>
+        <v>109.0733</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>119.23220000000001</v>
+        <v>109.0731</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>119.23220000000001</v>
+        <v>109.07299999999999</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>119.2324</v>
+        <v>109.0731</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>119.2328</v>
+        <v>109.07340000000001</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>119.2333</v>
+        <v>109.07380000000001</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>119.2341</v>
+        <v>109.0745</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>119.235</v>
+        <v>109.0753</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>119.23609999999999</v>
+        <v>109.0763</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>119.23739999999999</v>
+        <v>109.0775</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>119.2388</v>
+        <v>109.0788</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>119.2405</v>
+        <v>109.0804</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>119.2423</v>
+        <v>109.0821</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>119.2443</v>
+        <v>109.0839</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>119.24630000000001</v>
+        <v>109.0859</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>119.24850000000001</v>
+        <v>109.08799999999999</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>119.2508</v>
+        <v>109.0902</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>119.25320000000001</v>
+        <v>109.0925</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>119.2557</v>
+        <v>109.0949</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>119.2582</v>
+        <v>109.0973</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>119.2608</v>
+        <v>109.0998</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>119.2634</v>
+        <v>109.1023</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>119.26600000000001</v>
+        <v>109.1049</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>119.26860000000001</v>
+        <v>109.1074</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>119.27119999999999</v>
+        <v>109.11</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>119.27370000000001</v>
+        <v>109.1125</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>119.27630000000001</v>
+        <v>109.11499999999999</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>119.2787</v>
+        <v>109.1174</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>119.2811</v>
+        <v>109.1198</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>119.2834</v>
+        <v>109.1221</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>119.2856</v>
+        <v>109.12430000000001</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>119.2877</v>
+        <v>109.1264</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>119.2897</v>
+        <v>109.1284</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>119.29170000000001</v>
+        <v>109.13030000000001</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>119.29340000000001</v>
+        <v>109.13200000000001</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>119.29510000000001</v>
+        <v>109.1337</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>119.2967</v>
+        <v>109.1352</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>119.29810000000001</v>
+        <v>109.1367</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>119.29940000000001</v>
+        <v>109.1379</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>119.3006</v>
+        <v>109.1391</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>119.30159999999999</v>
+        <v>109.14019999999999</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>119.3026</v>
+        <v>109.14109999999999</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>119.3034</v>
+        <v>109.14190000000001</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>119.30410000000001</v>
+        <v>109.1426</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>119.3047</v>
+        <v>109.1431</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>119.3051</v>
+        <v>109.14360000000001</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>119.30549999999999</v>
+        <v>109.1439</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>119.3057</v>
+        <v>109.14409999999999</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>119.3058</v>
+        <v>109.1442</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>119.3058</v>
+        <v>109.1442</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>119.3056</v>
+        <v>109.14400000000001</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>119.30540000000001</v>
+        <v>109.1438</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>119.30500000000001</v>
+        <v>109.1434</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>119.30459999999999</v>
+        <v>109.143</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>119.304</v>
+        <v>109.1425</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>119.3034</v>
+        <v>109.1418</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>119.3027</v>
+        <v>109.14109999999999</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>119.3018</v>
+        <v>109.1403</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>119.3009</v>
+        <v>109.13939999999999</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="D121">
-        <v>119.3</v>
+        <v>109.13849999999999</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>119.29900000000001</v>
+        <v>109.1375</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="D123">
-        <v>119.2979</v>
+        <v>109.13639999999999</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>119.2967</v>
+        <v>109.1353</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="D125">
-        <v>119.29559999999999</v>
+        <v>109.1341</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>119.29430000000001</v>
+        <v>109.1328</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>119.2931</v>
+        <v>109.13160000000001</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="D128">
-        <v>119.29179999999999</v>
+        <v>109.13030000000001</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="D129">
-        <v>119.29049999999999</v>
+        <v>109.1289</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="D130">
-        <v>119.2891</v>
+        <v>109.1275</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>119.2878</v>
+        <v>109.12609999999999</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="D132">
-        <v>119.2864</v>
+        <v>109.1247</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
       <c r="D133">
-        <v>119.28489999999999</v>
+        <v>109.1233</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="D134">
-        <v>119.2835</v>
+        <v>109.12179999999999</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="D135">
-        <v>119.2821</v>
+        <v>109.1203</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="D136">
-        <v>119.28060000000001</v>
+        <v>109.11879999999999</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="D137">
-        <v>119.2792</v>
+        <v>109.1173</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>119.2777</v>
+        <v>109.11579999999999</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>119.2762</v>
+        <v>109.1142</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>119.2748</v>
+        <v>109.1127</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>119.27330000000001</v>
+        <v>109.11109999999999</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>119.2718</v>
+        <v>109.1096</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>119.27030000000001</v>
+        <v>109.108</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>119.2688</v>
+        <v>109.1065</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>119.26730000000001</v>
+        <v>109.1049</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>119.2658</v>
+        <v>109.10339999999999</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>119.26430000000001</v>
+        <v>109.1019</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>119.2628</v>
+        <v>109.10039999999999</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>119.26139999999999</v>
+        <v>109.0989</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>119.2599</v>
+        <v>109.09739999999999</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>119.2585</v>
+        <v>109.096</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>119.2572</v>
+        <v>109.0947</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>119.25579999999999</v>
+        <v>109.0934</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>119.2546</v>
+        <v>109.0921</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>119.2534</v>
+        <v>109.09099999999999</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>119.25230000000001</v>
+        <v>109.0899</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>119.2513</v>
+        <v>109.0889</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>119.2505</v>
+        <v>109.08799999999999</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>119.2497</v>
+        <v>109.0872</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>119.2491</v>
+        <v>109.0865</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>119.2486</v>
+        <v>109.086</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>119.2482</v>
+        <v>109.0856</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>119.248</v>
+        <v>109.08540000000001</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>119.248</v>
+        <v>109.0853</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>119.2482</v>
+        <v>109.08540000000001</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>119.24850000000001</v>
+        <v>109.0857</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>119.249</v>
+        <v>109.0861</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>119.2497</v>
+        <v>109.0868</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>119.2505</v>
+        <v>109.08759999999999</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>119.2516</v>
+        <v>109.0886</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>119.25279999999999</v>
+        <v>109.0898</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>119.2543</v>
+        <v>109.0911</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>119.25579999999999</v>
+        <v>109.0926</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>119.2576</v>
+        <v>109.0943</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>119.2595</v>
+        <v>109.09610000000001</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>119.2615</v>
+        <v>109.0981</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>119.2636</v>
+        <v>109.1002</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>119.2659</v>
+        <v>109.1023</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>119.26819999999999</v>
+        <v>109.1046</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>119.2706</v>
+        <v>109.107</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>119.273</v>
+        <v>109.10939999999999</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>119.27549999999999</v>
+        <v>109.11190000000001</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>119.27809999999999</v>
+        <v>109.1144</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>119.28060000000001</v>
+        <v>109.1169</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>119.2831</v>
+        <v>109.1194</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>119.28570000000001</v>
+        <v>109.1219</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>119.2882</v>
+        <v>109.12439999999999</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>119.2906</v>
+        <v>109.12690000000001</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>119.29300000000001</v>
+        <v>109.1292</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>119.2953</v>
+        <v>109.13160000000001</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>119.2975</v>
+        <v>109.13379999999999</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>119.2997</v>
+        <v>109.136</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>119.3017</v>
+        <v>109.13800000000001</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>119.3036</v>
+        <v>109.14</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>119.30549999999999</v>
+        <v>109.14190000000001</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>119.30719999999999</v>
+        <v>109.14360000000001</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>119.30880000000001</v>
+        <v>109.1452</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>119.3103</v>
+        <v>109.1467</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>119.3116</v>
+        <v>109.1481</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>119.3128</v>
+        <v>109.1493</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>119.3139</v>
+        <v>109.15049999999999</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>119.31489999999999</v>
+        <v>109.1515</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>119.3158</v>
+        <v>109.1524</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>119.3165</v>
+        <v>109.15309999999999</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>119.3172</v>
+        <v>109.1538</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>119.3177</v>
+        <v>109.15430000000001</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>119.3181</v>
+        <v>109.15470000000001</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>119.31829999999999</v>
+        <v>109.155</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>119.3185</v>
+        <v>109.1551</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>119.3185</v>
+        <v>109.15519999999999</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>119.3184</v>
+        <v>109.1551</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>119.3182</v>
+        <v>109.1549</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>119.31789999999999</v>
+        <v>109.1546</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>119.3175</v>
+        <v>109.1542</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>119.3169</v>
+        <v>109.1538</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>119.3163</v>
+        <v>109.1532</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>119.3156</v>
+        <v>109.1525</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>119.31480000000001</v>
+        <v>109.15170000000001</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>119.3139</v>
+        <v>109.15089999999999</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>119.3129</v>
+        <v>109.15</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="D221">
-        <v>119.31189999999999</v>
+        <v>109.149</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="D222">
-        <v>119.3108</v>
+        <v>109.14790000000001</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="D223">
-        <v>119.3096</v>
+        <v>109.1468</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="D224">
-        <v>119.30840000000001</v>
+        <v>109.1456</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="D225">
-        <v>119.30719999999999</v>
+        <v>109.1444</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="D226">
-        <v>119.30589999999999</v>
+        <v>109.1431</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="D227">
-        <v>119.30459999999999</v>
+        <v>109.1418</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="D228">
-        <v>119.3032</v>
+        <v>109.1404</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="D229">
-        <v>119.3018</v>
+        <v>109.139</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>0</v>
       </c>
       <c r="D230">
-        <v>119.3004</v>
+        <v>109.13760000000001</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="D231">
-        <v>119.29900000000001</v>
+        <v>109.1362</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="D232">
-        <v>119.2975</v>
+        <v>109.1347</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="D233">
-        <v>119.29600000000001</v>
+        <v>109.1332</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="D234">
-        <v>119.2946</v>
+        <v>109.1317</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="D235">
-        <v>119.29300000000001</v>
+        <v>109.1302</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="D236">
-        <v>119.2915</v>
+        <v>109.12869999999999</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="D237">
-        <v>119.29</v>
+        <v>109.1271</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>119.2885</v>
+        <v>109.1255</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>119.28700000000001</v>
+        <v>109.124</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>119.2854</v>
+        <v>109.1224</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>119.2839</v>
+        <v>109.1208</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>119.28230000000001</v>
+        <v>109.11920000000001</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>119.2807</v>
+        <v>109.1176</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>119.2792</v>
+        <v>109.116</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>119.27760000000001</v>
+        <v>109.1144</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>119.2761</v>
+        <v>109.11279999999999</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>119.2745</v>
+        <v>109.1113</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>119.273</v>
+        <v>109.1097</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>119.2715</v>
+        <v>109.1082</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>119.27</v>
+        <v>109.1067</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>119.2685</v>
+        <v>109.1053</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>119.2671</v>
+        <v>109.1039</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>119.2657</v>
+        <v>109.1026</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>119.26439999999999</v>
+        <v>109.10129999999999</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>119.2632</v>
+        <v>109.1001</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>119.262</v>
+        <v>109.0989</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>119.261</v>
+        <v>109.0979</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>119.26</v>
+        <v>109.09699999999999</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>119.25920000000001</v>
+        <v>109.09610000000001</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>119.2585</v>
+        <v>109.0954</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>119.258</v>
+        <v>109.0949</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>119.2576</v>
+        <v>109.09439999999999</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>119.2573</v>
+        <v>109.0942</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>119.2572</v>
+        <v>109.09399999999999</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>119.2573</v>
+        <v>109.0941</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>119.2576</v>
+        <v>109.09439999999999</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>119.2581</v>
+        <v>109.09480000000001</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>119.2587</v>
+        <v>109.0954</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>119.2595</v>
+        <v>109.0962</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>119.26049999999999</v>
+        <v>109.0971</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>119.2617</v>
+        <v>109.09829999999999</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>119.26309999999999</v>
+        <v>109.0996</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>119.2646</v>
+        <v>109.1011</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>119.2663</v>
+        <v>109.1027</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>119.26819999999999</v>
+        <v>109.1045</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>119.2701</v>
+        <v>109.10639999999999</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>119.2722</v>
+        <v>109.10850000000001</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>119.2744</v>
+        <v>109.11060000000001</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>119.27670000000001</v>
+        <v>109.11279999999999</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>119.279</v>
+        <v>109.1152</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>119.2814</v>
+        <v>109.1176</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>119.2839</v>
+        <v>109.12</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>119.2863</v>
+        <v>109.1225</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>119.28879999999999</v>
+        <v>109.1249</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>119.29130000000001</v>
+        <v>109.12739999999999</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>119.2938</v>
+        <v>109.12990000000001</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>119.2962</v>
+        <v>109.1324</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>119.29859999999999</v>
+        <v>109.1348</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>119.301</v>
+        <v>109.1371</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>119.3032</v>
+        <v>109.13939999999999</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>119.30540000000001</v>
+        <v>109.1417</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>119.3075</v>
+        <v>109.1438</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>119.3095</v>
+        <v>109.14579999999999</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>119.31140000000001</v>
+        <v>109.1477</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>119.31319999999999</v>
+        <v>109.14960000000001</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>119.31489999999999</v>
+        <v>109.15130000000001</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>119.3164</v>
+        <v>109.1529</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>119.31780000000001</v>
+        <v>109.15430000000001</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>119.3192</v>
+        <v>109.1557</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>119.3203</v>
+        <v>109.15689999999999</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>119.3214</v>
+        <v>109.158</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>119.3223</v>
+        <v>109.15900000000001</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>119.3232</v>
+        <v>109.1598</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/10_LTAN06_800km_HOT_MY_ALL_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/10_LTAN06_800km_HOT_MY_ALL_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85D159B1-F452-484A-B692-32DB68F7C193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55E607F2-7F87-4023-8A3A-6CD94FD6E7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{CC77782E-B6AE-4BCD-9A3A-99045480BBC6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{40E015DB-54EB-4BAC-A405-2E42B1EB8B03}"/>
   </bookViews>
   <sheets>
     <sheet name="10_LTAN06_800km_HOT_MY_ALL_HEAT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82695578-993A-4574-BBB1-D3D440E83272}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{918A2541-3A38-41CB-9282-9972F270D662}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/10_LTAN06_800km_HOT_MY_ALL_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/10_LTAN06_800km_HOT_MY_ALL_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55E607F2-7F87-4023-8A3A-6CD94FD6E7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{234A06D1-7582-4C48-9273-8328D562B069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{40E015DB-54EB-4BAC-A405-2E42B1EB8B03}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{9815790B-515C-4B63-A988-FB7BC19B16B3}"/>
   </bookViews>
   <sheets>
     <sheet name="10_LTAN06_800km_HOT_MY_ALL_HEAT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{918A2541-3A38-41CB-9282-9972F270D662}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89359E49-EBEA-44C3-B1DF-BD0CF9D0718A}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
